--- a/data/trans_bre/P12_3_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P12_3_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,63</t>
+          <t>0,64; 5,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,84</t>
+          <t>-3,69; 1,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,78</t>
+          <t>1,1; 6,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 7,73</t>
+          <t>-2,84; 7,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 423,68</t>
+          <t>3,39; 376,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,49; 70,88</t>
+          <t>-64,69; 51,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 673,96</t>
+          <t>7,54; 846,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,18; 354,78</t>
+          <t>-55,39; 315,79</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,4</t>
+          <t>2,65; 7,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,78</t>
+          <t>-1,51; 3,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,51</t>
+          <t>-1,77; 3,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 5,21</t>
+          <t>-4,73; 4,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,71; 303,3</t>
+          <t>57,43; 334,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 104,33</t>
+          <t>-26,39; 102,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,27; 86,57</t>
+          <t>-27,73; 86,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,0; 83,25</t>
+          <t>-42,23; 71,37</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,37</t>
+          <t>-0,44; 4,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,46</t>
+          <t>2,18; 8,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,01</t>
+          <t>-1,3; 3,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 4,25</t>
+          <t>-1,7; 4,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 122,49</t>
+          <t>-9,17; 132,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,34; 166,15</t>
+          <t>26,97; 161,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 110,71</t>
+          <t>-21,48; 108,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 72,17</t>
+          <t>-17,82; 79,8</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,19</t>
+          <t>1,19; 7,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,48</t>
+          <t>3,45; 11,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,76</t>
+          <t>-3,31; 3,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 8,98</t>
+          <t>-1,6; 8,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,52; 222,86</t>
+          <t>16,98; 245,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,35; 150,02</t>
+          <t>31,09; 154,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 42,26</t>
+          <t>-25,73; 43,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 221,45</t>
+          <t>-12,41; 220,88</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 6,4</t>
+          <t>-1,31; 6,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,5</t>
+          <t>0,62; 9,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 12,65</t>
+          <t>3,16; 12,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 8,64</t>
+          <t>1,89; 9,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 119,56</t>
+          <t>-16,92; 122,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 111,86</t>
+          <t>3,57; 105,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,74; 154,23</t>
+          <t>25,12; 154,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,6; 85,64</t>
+          <t>12,86; 89,84</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 7,86</t>
+          <t>-2,27; 8,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 12,22</t>
+          <t>0,41; 11,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,69</t>
+          <t>3,6; 13,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 6,01</t>
+          <t>-9,54; 6,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 96,52</t>
+          <t>-17,36; 101,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 126,33</t>
+          <t>2,69; 124,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,04; 262,79</t>
+          <t>31,01; 264,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 46,55</t>
+          <t>-61,86; 48,71</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 7,33</t>
+          <t>-3,46; 7,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 17,14</t>
+          <t>4,3; 17,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 16,76</t>
+          <t>4,69; 17,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 10,51</t>
+          <t>1,23; 10,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 121,69</t>
+          <t>-30,57; 120,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,29; 156,22</t>
+          <t>20,84; 149,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,67; 136,39</t>
+          <t>26,02; 146,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,66; 64,29</t>
+          <t>5,43; 63,6</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,66</t>
+          <t>2,2; 4,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,67</t>
+          <t>3,58; 6,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,9</t>
+          <t>2,9; 5,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,62</t>
+          <t>0,64; 5,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,51; 103,14</t>
+          <t>38,81; 104,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,33; 88,46</t>
+          <t>40,88; 90,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,41; 85,18</t>
+          <t>35,64; 85,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,54; 69,49</t>
+          <t>7,71; 65,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_3_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P12_3_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,52</t>
+          <t>0,62; 5,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,34</t>
+          <t>-3,81; 1,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,39</t>
+          <t>0,89; 5,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 7,53</t>
+          <t>-4,08; 6,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 376,87</t>
+          <t>12,5; 402,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-64,69; 51,17</t>
+          <t>-65,68; 51,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 846,06</t>
+          <t>22,94; 739,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,39; 315,79</t>
+          <t>-52,05; 220,65</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,96</t>
+          <t>2,46; 7,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,88</t>
+          <t>-1,28; 3,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,64</t>
+          <t>-1,95; 3,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 4,51</t>
+          <t>-3,01; 6,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,43; 334,16</t>
+          <t>54,0; 325,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 102,51</t>
+          <t>-23,25; 100,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 86,05</t>
+          <t>-30,09; 85,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 71,37</t>
+          <t>-28,27; 99,04</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 4,6</t>
+          <t>-0,59; 4,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,22</t>
+          <t>1,57; 8,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,57</t>
+          <t>-1,08; 3,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,63</t>
+          <t>-0,83; 5,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 132,77</t>
+          <t>-11,2; 131,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,97; 161,39</t>
+          <t>17,8; 156,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 108,99</t>
+          <t>-19,48; 104,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 79,8</t>
+          <t>-9,32; 86,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,39</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,6</t>
+          <t>1,02; 7,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 11,46</t>
+          <t>3,77; 11,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 3,91</t>
+          <t>-3,32; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 8,71</t>
+          <t>-1,12; 5,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 245,44</t>
+          <t>13,56; 234,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,09; 154,19</t>
+          <t>34,33; 157,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,73; 43,2</t>
+          <t>-25,38; 46,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 220,88</t>
+          <t>-9,26; 63,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 6,45</t>
+          <t>-1,5; 6,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 9,94</t>
+          <t>0,14; 9,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 12,56</t>
+          <t>3,34; 12,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,06</t>
+          <t>1,96; 8,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 122,83</t>
+          <t>-18,68; 116,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 105,87</t>
+          <t>0,77; 109,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,12; 154,39</t>
+          <t>23,08; 155,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,86; 89,84</t>
+          <t>14,56; 88,51</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-10,55%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 8,01</t>
+          <t>-2,71; 7,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 11,88</t>
+          <t>0,45; 11,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,6; 13,69</t>
+          <t>3,55; 13,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 6,27</t>
+          <t>1,79; 9,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 101,07</t>
+          <t>-18,68; 97,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 124,12</t>
+          <t>1,12; 118,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,01; 264,19</t>
+          <t>38,49; 261,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,86; 48,71</t>
+          <t>11,69; 88,77</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,1</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 7,31</t>
+          <t>-3,63; 6,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 17,46</t>
+          <t>4,1; 17,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,69; 17,31</t>
+          <t>3,94; 17,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,89</t>
+          <t>0,9; 11,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 120,64</t>
+          <t>-31,84; 116,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,84; 149,09</t>
+          <t>20,24; 151,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,02; 146,68</t>
+          <t>23,44; 140,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 63,6</t>
+          <t>3,65; 64,07</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,7</t>
+          <t>2,29; 4,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,77</t>
+          <t>3,67; 6,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,75</t>
+          <t>2,86; 5,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,47</t>
+          <t>2,66; 5,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>38,81; 104,09</t>
+          <t>41,28; 107,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,88; 90,04</t>
+          <t>42,26; 92,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,64; 85,26</t>
+          <t>34,84; 86,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,71; 65,24</t>
+          <t>23,3; 57,53</t>
         </is>
       </c>
     </row>
